--- a/research/traditional_assets/database/data/mauritius/mauritius_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
       <c r="E2">
-        <v>-0.11395</v>
+        <v>0.067</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>14.5</v>
+        <v>20.93</v>
       </c>
       <c r="L2">
-        <v>0.2369668246445498</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M2">
-        <v>3.02</v>
+        <v>7.044</v>
       </c>
       <c r="N2">
-        <v>0.01552699228791774</v>
+        <v>0.03504477611940299</v>
       </c>
       <c r="O2">
-        <v>0.2082758620689655</v>
+        <v>0.3365504061156235</v>
       </c>
       <c r="P2">
-        <v>3.02</v>
+        <v>7.044</v>
       </c>
       <c r="Q2">
-        <v>0.01552699228791774</v>
+        <v>0.03504477611940299</v>
       </c>
       <c r="R2">
-        <v>0.2082758620689655</v>
+        <v>0.3365504061156235</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.609999999999999</v>
+        <v>16.36</v>
       </c>
       <c r="V2">
-        <v>0.04940874035989717</v>
+        <v>0.08139303482587064</v>
       </c>
       <c r="W2">
-        <v>0.06310919735967173</v>
+        <v>0.08653157521222594</v>
       </c>
       <c r="X2">
-        <v>0.03615709265996721</v>
+        <v>0.06707504281502384</v>
       </c>
       <c r="Y2">
-        <v>0.02695210469970451</v>
+        <v>0.0194565323972021</v>
       </c>
       <c r="Z2">
-        <v>0.1234989000343109</v>
+        <v>0.1247590852192573</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03394661838932955</v>
+        <v>0.06814664591332217</v>
       </c>
       <c r="AC2">
-        <v>-0.03394661838932955</v>
+        <v>-0.06814664591332217</v>
       </c>
       <c r="AD2">
-        <v>250.5</v>
+        <v>277</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>250.5</v>
+        <v>277</v>
       </c>
       <c r="AG2">
-        <v>240.89</v>
+        <v>260.64</v>
       </c>
       <c r="AH2">
-        <v>0.5629213483146067</v>
+        <v>0.5794979079497908</v>
       </c>
       <c r="AI2">
-        <v>0.4883992981087932</v>
+        <v>0.5122041420118344</v>
       </c>
       <c r="AJ2">
-        <v>0.5532740761156664</v>
+        <v>0.5645957889264361</v>
       </c>
       <c r="AK2">
-        <v>0.478630610582368</v>
+        <v>0.4969872626039204</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>-0.139</v>
+        <v>0.407</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,28 +725,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>7.83</v>
       </c>
       <c r="L3">
-        <v>0.5523590333716916</v>
+        <v>1.188163884673748</v>
       </c>
       <c r="M3">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="N3">
-        <v>0.02981366459627329</v>
+        <v>0.04010025062656642</v>
       </c>
       <c r="O3">
-        <v>0.3</v>
+        <v>0.2043422733077906</v>
       </c>
       <c r="P3">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>0.02981366459627329</v>
+        <v>0.04010025062656642</v>
       </c>
       <c r="R3">
-        <v>0.3</v>
+        <v>0.2043422733077906</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="V3">
-        <v>0.03436853002070393</v>
+        <v>0.03659147869674186</v>
       </c>
       <c r="W3">
-        <v>0.03418803418803418</v>
+        <v>0.05028901734104047</v>
       </c>
       <c r="X3">
-        <v>0.03001604657474312</v>
+        <v>0.05879005284161001</v>
       </c>
       <c r="Y3">
-        <v>0.004171987613291062</v>
+        <v>-0.008501035500569541</v>
       </c>
       <c r="Z3">
-        <v>0.05809988634084375</v>
+        <v>0.03859669673187303</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03093976184898046</v>
+        <v>0.06249647663909511</v>
       </c>
       <c r="AC3">
-        <v>-0.03093976184898046</v>
+        <v>-0.06249647663909511</v>
       </c>
       <c r="AD3">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="AG3">
-        <v>15.04</v>
+        <v>12.84</v>
       </c>
       <c r="AH3">
-        <v>0.2569230769230769</v>
+        <v>0.2638376383763837</v>
       </c>
       <c r="AI3">
-        <v>0.0968677494199536</v>
+        <v>0.08436578171091445</v>
       </c>
       <c r="AJ3">
-        <v>0.2374486896116198</v>
+        <v>0.2434584755403868</v>
       </c>
       <c r="AK3">
-        <v>0.08808715005271173</v>
+        <v>0.07641037848131398</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
       <c r="E4">
-        <v>-0.08890000000000001</v>
+        <v>-0.273</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,28 +847,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>9.699999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="L4">
-        <v>0.1847619047619047</v>
+        <v>0.2330960854092526</v>
       </c>
       <c r="M4">
-        <v>1.58</v>
+        <v>5.444</v>
       </c>
       <c r="N4">
-        <v>0.01080711354309166</v>
+        <v>0.03379267535692117</v>
       </c>
       <c r="O4">
-        <v>0.1628865979381444</v>
+        <v>0.4155725190839695</v>
       </c>
       <c r="P4">
-        <v>1.58</v>
+        <v>5.444</v>
       </c>
       <c r="Q4">
-        <v>0.01080711354309166</v>
+        <v>0.03379267535692117</v>
       </c>
       <c r="R4">
-        <v>0.1628865979381444</v>
+        <v>0.4155725190839695</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -877,55 +877,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>7.95</v>
+        <v>14.9</v>
       </c>
       <c r="V4">
-        <v>0.05437756497948017</v>
+        <v>0.09248913718187461</v>
       </c>
       <c r="W4">
-        <v>0.09203036053130928</v>
+        <v>0.1227741330834114</v>
       </c>
       <c r="X4">
-        <v>0.0422981387451913</v>
+        <v>0.07536003278843767</v>
       </c>
       <c r="Y4">
-        <v>0.04973222178611798</v>
+        <v>0.04741410029497375</v>
       </c>
       <c r="Z4">
-        <v>0.1517779705117086</v>
+        <v>0.1689971432867238</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03695347492967864</v>
+        <v>0.07379681518754923</v>
       </c>
       <c r="AC4">
-        <v>-0.03695347492967864</v>
+        <v>-0.07379681518754923</v>
       </c>
       <c r="AD4">
-        <v>233.8</v>
+        <v>262.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>233.8</v>
+        <v>262.7</v>
       </c>
       <c r="AG4">
-        <v>225.85</v>
+        <v>247.8</v>
       </c>
       <c r="AH4">
-        <v>0.6152631578947368</v>
+        <v>0.6198678621991506</v>
       </c>
       <c r="AI4">
-        <v>0.6866372980910426</v>
+        <v>0.7075141395098303</v>
       </c>
       <c r="AJ4">
-        <v>0.6070420642386777</v>
+        <v>0.6060161408657373</v>
       </c>
       <c r="AK4">
-        <v>0.6791459930837469</v>
+        <v>0.6952861952861953</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/mauritius/mauritius_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.141</v>
+        <v>0.187</v>
       </c>
       <c r="E2">
-        <v>0.067</v>
+        <v>0.223</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>20.93</v>
+        <v>29.72</v>
       </c>
       <c r="L2">
-        <v>0.3333333333333333</v>
+        <v>0.39823127428648</v>
       </c>
       <c r="M2">
-        <v>7.044</v>
+        <v>10.2365</v>
       </c>
       <c r="N2">
-        <v>0.03504477611940299</v>
+        <v>0.04983690360272639</v>
       </c>
       <c r="O2">
-        <v>0.3365504061156235</v>
+        <v>0.3444313593539704</v>
       </c>
       <c r="P2">
-        <v>7.044</v>
+        <v>10.2365</v>
       </c>
       <c r="Q2">
-        <v>0.03504477611940299</v>
+        <v>0.04983690360272639</v>
       </c>
       <c r="R2">
-        <v>0.3365504061156235</v>
+        <v>0.3444313593539704</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.36</v>
+        <v>17.31</v>
       </c>
       <c r="V2">
-        <v>0.08139303482587064</v>
+        <v>0.08427458617332036</v>
       </c>
       <c r="W2">
-        <v>0.08653157521222594</v>
+        <v>0.1256073076265877</v>
       </c>
       <c r="X2">
-        <v>0.06707504281502384</v>
+        <v>0.07497864714270105</v>
       </c>
       <c r="Y2">
-        <v>0.0194565323972021</v>
+        <v>0.05062866048388664</v>
       </c>
       <c r="Z2">
-        <v>0.1247590852192573</v>
+        <v>0.1423801892551892</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06814664591332217</v>
+        <v>0.06629830048740912</v>
       </c>
       <c r="AC2">
-        <v>-0.06814664591332217</v>
+        <v>-0.06629830048740912</v>
       </c>
       <c r="AD2">
-        <v>277</v>
+        <v>319.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>277</v>
+        <v>319.9</v>
       </c>
       <c r="AG2">
-        <v>260.64</v>
+        <v>302.59</v>
       </c>
       <c r="AH2">
-        <v>0.5794979079497908</v>
+        <v>0.6089853417094994</v>
       </c>
       <c r="AI2">
-        <v>0.5122041420118344</v>
+        <v>0.5159677419354838</v>
       </c>
       <c r="AJ2">
-        <v>0.5645957889264361</v>
+        <v>0.5956613319159826</v>
       </c>
       <c r="AK2">
-        <v>0.4969872626039204</v>
+        <v>0.5020657386052531</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -709,9 +709,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.407</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -725,28 +722,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>7.83</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L3">
-        <v>1.188163884673748</v>
+        <v>0.8992248062015503</v>
       </c>
       <c r="M3">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="N3">
-        <v>0.04010025062656642</v>
+        <v>0.03687002652519893</v>
       </c>
       <c r="O3">
-        <v>0.2043422733077906</v>
+        <v>0.1711822660098522</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="Q3">
-        <v>0.04010025062656642</v>
+        <v>0.03687002652519893</v>
       </c>
       <c r="R3">
-        <v>0.2043422733077906</v>
+        <v>0.1711822660098522</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.46</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="V3">
-        <v>0.03659147869674186</v>
+        <v>0.2217506631299734</v>
       </c>
       <c r="W3">
-        <v>0.05028901734104047</v>
+        <v>0.05231958762886598</v>
       </c>
       <c r="X3">
-        <v>0.05879005284161001</v>
+        <v>0.06342331600936366</v>
       </c>
       <c r="Y3">
-        <v>-0.008501035500569541</v>
+        <v>-0.01110372838049768</v>
       </c>
       <c r="Z3">
-        <v>0.03859669673187303</v>
+        <v>0.05373720542727922</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06249647663909511</v>
+        <v>0.0640799308439543</v>
       </c>
       <c r="AC3">
-        <v>-0.06249647663909511</v>
+        <v>-0.0640799308439543</v>
       </c>
       <c r="AD3">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="AG3">
-        <v>12.84</v>
+        <v>5.640000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2638376383763837</v>
+        <v>0.2707930367504836</v>
       </c>
       <c r="AI3">
-        <v>0.08436578171091445</v>
+        <v>0.07637752318603382</v>
       </c>
       <c r="AJ3">
-        <v>0.2434584755403868</v>
+        <v>0.1301338255652977</v>
       </c>
       <c r="AK3">
-        <v>0.07641037848131398</v>
+        <v>0.03223962501429062</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.141</v>
+        <v>0.187</v>
       </c>
       <c r="E4">
-        <v>-0.273</v>
+        <v>0.223</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>13.1</v>
+        <v>21.6</v>
       </c>
       <c r="L4">
-        <v>0.2330960854092526</v>
+        <v>0.3292682926829269</v>
       </c>
       <c r="M4">
-        <v>5.444</v>
+        <v>8.846499999999999</v>
       </c>
       <c r="N4">
-        <v>0.03379267535692117</v>
+        <v>0.05275193798449612</v>
       </c>
       <c r="O4">
-        <v>0.4155725190839695</v>
+        <v>0.4095601851851851</v>
       </c>
       <c r="P4">
-        <v>5.444</v>
+        <v>8.846499999999999</v>
       </c>
       <c r="Q4">
-        <v>0.03379267535692117</v>
+        <v>0.05275193798449612</v>
       </c>
       <c r="R4">
-        <v>0.4155725190839695</v>
+        <v>0.4095601851851851</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -877,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>14.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="V4">
-        <v>0.09248913718187461</v>
+        <v>0.05336911150864639</v>
       </c>
       <c r="W4">
-        <v>0.1227741330834114</v>
+        <v>0.1988950276243094</v>
       </c>
       <c r="X4">
-        <v>0.07536003278843767</v>
+        <v>0.08653397827603845</v>
       </c>
       <c r="Y4">
-        <v>0.04741410029497375</v>
+        <v>0.112361049348271</v>
       </c>
       <c r="Z4">
-        <v>0.1689971432867238</v>
+        <v>0.18420757048186</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07379681518754923</v>
+        <v>0.06851667013086392</v>
       </c>
       <c r="AC4">
-        <v>-0.07379681518754923</v>
+        <v>-0.06851667013086392</v>
       </c>
       <c r="AD4">
-        <v>262.7</v>
+        <v>305.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>262.7</v>
+        <v>305.9</v>
       </c>
       <c r="AG4">
-        <v>247.8</v>
+        <v>296.95</v>
       </c>
       <c r="AH4">
-        <v>0.6198678621991506</v>
+        <v>0.6459037162162162</v>
       </c>
       <c r="AI4">
-        <v>0.7075141395098303</v>
+        <v>0.7004808793221892</v>
       </c>
       <c r="AJ4">
-        <v>0.6060161408657373</v>
+        <v>0.6390831808888411</v>
       </c>
       <c r="AK4">
-        <v>0.6952861952861953</v>
+        <v>0.6942139099941554</v>
       </c>
       <c r="AL4">
         <v>0</v>
